--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/antofagasta.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/antofagasta.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>21666.96</v>
+        <v>21744.29</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5348.71</v>
+        <v>5366.3</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>29117.37</v>
+        <v>28997.36</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>8637.92</v>
+        <v>8624.530000000001</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>26868.23</v>
+        <v>26826.59</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1624.19</v>
+        <v>1632.58</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>15213.69</v>
+        <v>15321.06</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1053.4</v>
+        <v>1040.02</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2653.64</v>
+        <v>2644.13</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>8822.1</v>
+        <v>8815.01</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4204.52</v>
+        <v>4223.58</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3536.97</v>
+        <v>3553</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2731.54</v>
+        <v>2738.78</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>849.48</v>
+        <v>851.73</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>857.27</v>
+        <v>859.54</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>13351.94</v>
+        <v>13387.34</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>12102.95</v>
+        <v>12206.38</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1605.14</v>
+        <v>1613.92</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2308.26</v>
+        <v>2306.68</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>40220.44</v>
+        <v>40484.04</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1017.33</v>
+        <v>1048.18</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>4179.32</v>
+        <v>4191.42</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2163.9</v>
+        <v>2178.97</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>31447.99</v>
+        <v>31394.09</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2444.43</v>
+        <v>2446.79</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2044.84</v>
+        <v>2018.51</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>18324.14</v>
+        <v>18194.83</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2463</v>
+        <v>2445.62</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>7100.63</v>
+        <v>7068.88</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2629.21</v>
+        <v>2614.11</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>37349.3</v>
+        <v>37110.02</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1760.94</v>
+        <v>1753.36</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>10883.63</v>
+        <v>10630.38</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>15158.96</v>
+        <v>14860.01</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1134.65</v>
+        <v>1112.28</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>13604.24</v>
+        <v>13771.67</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>874.42</v>
+        <v>886.0599999999999</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2425.85</v>
+        <v>2457.51</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>7966.43</v>
+        <v>7898.48</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>830.8200000000001</v>
+        <v>823.73</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>25729</v>
+        <v>25664.04</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>12166.32</v>
+        <v>12033.97</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>12990.63</v>
+        <v>12961.15</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>32009.65</v>
+        <v>32166.89</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5725.43</v>
+        <v>5744.42</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>8581.17</v>
+        <v>8608.48</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3686.38</v>
+        <v>3739.13</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>8666.950000000001</v>
+        <v>8813.530000000001</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>11802.41</v>
+        <v>12002.02</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>27638.79</v>
+        <v>27898.02</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>791.67</v>
+        <v>781.13</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>4787.02</v>
+        <v>4835.17</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>812</v>
+        <v>817.29</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1130.79</v>
+        <v>1117.63</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/antofagasta.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3834-271-CM25</t>
+          <t>650-67-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.814.000-8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>21744.29</v>
+        <v>1122.71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3834-275-CM25</t>
+          <t>697036-89-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5366.3</v>
+        <v>1108.35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2429-2957-CM25</t>
+          <t>558869-227-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.882.403-7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>28997.36</v>
+        <v>1524.07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1775-67-CM25</t>
+          <t>558869-229-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.804.004-8</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE ANTOFAGASTA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>SEGURYCEL SA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>99.510.910-7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>8624.530000000001</v>
+        <v>5593.81</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2429-2971-CM25</t>
+          <t>558869-233-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>26826.59</v>
+        <v>1071.21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1230848-314-CM25</t>
+          <t>3834-271-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,22 +834,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1632.58</v>
+        <v>21744.29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2429-2993-CM25</t>
+          <t>3834-275-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>15321.06</v>
+        <v>5366.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1077908-315-CM25</t>
+          <t>2429-2957-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1040.02</v>
+        <v>28997.36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1983-89-CM25</t>
+          <t>1775-67-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.701.011-0</t>
+          <t>60.804.004-8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2644.13</v>
+        <v>8624.530000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1775-73-CM25</t>
+          <t>2429-2971-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.804.004-8</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>8815.01</v>
+        <v>26826.59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>778989-204-CM25</t>
+          <t>1230848-314-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>65.081.190-9</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4223.58</v>
+        <v>1632.58</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2429-3130-CM25</t>
+          <t>2429-2993-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3553</v>
+        <v>15321.06</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2385-1218-CM25</t>
+          <t>1077908-315-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.362.622-7</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2738.78</v>
+        <v>1040.02</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2385-1217-CM25</t>
+          <t>1983-89-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>60.701.011-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>Servicio Nacional de Pesca y Acuicultura</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>851.73</v>
+        <v>2644.13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2385-1215-CM25</t>
+          <t>1775-73-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>60.804.004-8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TECNOQUIM SPA</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.378.846-6</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>859.54</v>
+        <v>8815.01</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1233623-1545-CM25</t>
+          <t>778989-204-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>65.081.190-9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>3a Briagada Acorazada "La Concepción"</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>13387.34</v>
+        <v>4223.58</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2429-3194-CM25</t>
+          <t>2429-3130-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>12206.38</v>
+        <v>3553</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1233623-1396-CM25</t>
+          <t>1233623-1545-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1613.92</v>
+        <v>13387.34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3858-23-CM26</t>
+          <t>2385-1215-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,27 +1622,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>TECNOQUIM SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.378.846-6</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2306.68</v>
+        <v>859.54</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2429-32-CM26</t>
+          <t>2385-1217-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>40484.04</v>
+        <v>851.73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>707415-10-CM26</t>
+          <t>2385-1218-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,27 +1744,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.362.622-7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1048.18</v>
+        <v>2738.78</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3858-57-CM26</t>
+          <t>2429-3194-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>4191.42</v>
+        <v>12206.38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2605-10-CM26</t>
+          <t>1233623-1396-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2178.97</v>
+        <v>1613.92</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2430-30-CM26</t>
+          <t>3858-23-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>31394.09</v>
+        <v>2306.68</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>778989-19-CM26</t>
+          <t>2429-32-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,27 +1988,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>65.081.190-9</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2446.79</v>
+        <v>40484.04</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2385-127-CM26</t>
+          <t>707415-10-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2018.51</v>
+        <v>1048.18</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>769-128-CM26</t>
+          <t>3858-57-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,27 +2110,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>18194.83</v>
+        <v>4191.42</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1113265-11-CM26</t>
+          <t>2605-10-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>62.000.770-6</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2445.62</v>
+        <v>2178.97</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1079454-65-CM26</t>
+          <t>2430-30-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>7068.88</v>
+        <v>31394.09</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2429-254-CM26</t>
+          <t>778989-19-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,27 +2293,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>65.081.190-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>3a Briagada Acorazada "La Concepción"</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2614.11</v>
+        <v>2446.79</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1288419-18-CM26</t>
+          <t>2385-127-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,22 +2359,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Gestión del Riesgo de Desastres</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>INVERSIONES CHILE LIMITADA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.795.374-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>37110.02</v>
+        <v>2018.51</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>993-49-CM26</t>
+          <t>1113265-11-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,22 +2420,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.770-6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1753.36</v>
+        <v>2445.62</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2385-193-CM26</t>
+          <t>769-128-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>10630.38</v>
+        <v>18194.83</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3506-219-CM26</t>
+          <t>1079454-65-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,27 +2537,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>SECCIÓN COMPRAS II ZONA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>14860.01</v>
+        <v>7068.88</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3506-220-CM26</t>
+          <t>2429-254-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1112.28</v>
+        <v>2614.11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2429-347-CM26</t>
+          <t>1288419-18-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,27 +2659,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>Gestión del Riesgo de Desastres</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>INVERSIONES CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>77.795.374-5</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>13771.67</v>
+        <v>37110.02</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>778989-66-CM26</t>
+          <t>993-49-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,27 +2720,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>65.081.190-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>886.0599999999999</v>
+        <v>1753.36</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>778989-69-CM26</t>
+          <t>2385-193-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>65.081.190-9</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2457.51</v>
+        <v>10630.38</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3246-117-CM26</t>
+          <t>3506-219-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.103.019-3</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>ALA BASE N°1</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>7898.48</v>
+        <v>14860.01</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3246-118-CM26</t>
+          <t>3506-220-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.103.019-3</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>ALA BASE N°1</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>823.73</v>
+        <v>1112.28</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2429-500-CM26</t>
+          <t>2429-347-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>25664.04</v>
+        <v>13771.67</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1697-124-CM26</t>
+          <t>778989-66-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>65.081.190-9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>3a Briagada Acorazada "La Concepción"</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>12033.97</v>
+        <v>886.0599999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1261592-490-CM26</t>
+          <t>778989-69-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>65.081.190-9</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>3a Briagada Acorazada "La Concepción"</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>12961.15</v>
+        <v>2457.51</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2385-365-CM26</t>
+          <t>3246-118-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>61.103.019-3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>ALA BASE N°1</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>32166.89</v>
+        <v>823.73</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2429-578-CM26</t>
+          <t>3246-117-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.103.019-3</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>ALA BASE N°1</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIALIZADORA WAY SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.532.399-1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5744.42</v>
+        <v>7898.48</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>769-320-CM26</t>
+          <t>2429-500-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>8608.48</v>
+        <v>25664.04</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2429-614-CM26</t>
+          <t>1697-124-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3739.13</v>
+        <v>12033.97</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1116003-22-CM26</t>
+          <t>1261592-490-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,27 +3391,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>8813.530000000001</v>
+        <v>12961.15</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1116003-23-CM26</t>
+          <t>2385-365-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>LORENZINI PAGLIETTINI Y CIA LTDA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>80.565.500-3</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>12002.02</v>
+        <v>32166.89</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2429-666-CM26</t>
+          <t>2429-578-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>27898.02</v>
+        <v>5744.42</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1079454-263-CM26</t>
+          <t>769-320-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3574,27 +3574,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>781.13</v>
+        <v>8608.48</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>778992-183-CM26</t>
+          <t>2429-614-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3635,27 +3635,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>4835.17</v>
+        <v>3739.13</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>930-139-CM26</t>
+          <t>1116003-22-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3696,27 +3696,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>817.29</v>
+        <v>8813.530000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4051-140-CM26</t>
+          <t>1116003-23-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>LORENZINI PAGLIETTINI Y CIA LTDA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>80.565.500-3</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,6 +3802,311 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
+        <v>12002.02</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2429-666-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>27898.02</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1079454-263-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>61.978.660-2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS II ZONA</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>781.13</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>778992-183-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>61.953.000-4</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>4835.17</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>930-139-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>817.29</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>4051-140-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>69.252.600-7</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>SOSEG SPA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>76.897.534-5</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
         <v>1117.63</v>
       </c>
     </row>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/antofagasta.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/antofagasta.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Antofagasta" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Antofagasta" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>650-67-CM25</t>
+          <t>4291-104-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.814.000-8</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1122.71</v>
+        <v>16968.04</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>697036-89-CM25</t>
+          <t>558869-7-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1108.35</v>
+        <v>801.24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>558869-227-CM25</t>
+          <t>1261592-58-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Francisco javier</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.882.403-7</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1524.07</v>
+        <v>33868.15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>558869-229-CM25</t>
+          <t>3274-20-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SEGURYCEL SA</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>99.510.910-7</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5593.81</v>
+        <v>1977.82</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>558869-233-CM25</t>
+          <t>2429-1555-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1071.21</v>
+        <v>33819.65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3834-271-CM25</t>
+          <t>2429-1607-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>21744.29</v>
+        <v>14424.63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3834-275-CM25</t>
+          <t>2429-1606-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5366.3</v>
+        <v>35120.46</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2429-2957-CM25</t>
+          <t>2429-1615-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>28997.36</v>
+        <v>22992.92</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1775-67-CM25</t>
+          <t>1077908-37-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.804.004-8</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE ANTOFAGASTA</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>8624.530000000001</v>
+        <v>2467.95</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2429-2971-CM25</t>
+          <t>2215-311-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>26826.59</v>
+        <v>14242.78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1230848-314-CM25</t>
+          <t>769-4236-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1632.58</v>
+        <v>8348.959999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2429-2993-CM25</t>
+          <t>1113265-20-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>62.000.770-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>15321.06</v>
+        <v>729.45</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1077908-315-CM25</t>
+          <t>2605-12-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1040.02</v>
+        <v>736.14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1983-89-CM25</t>
+          <t>2605-7-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.701.011-0</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2644.13</v>
+        <v>1386.53</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1775-73-CM25</t>
+          <t>2430-45-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.804.004-8</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>8815.01</v>
+        <v>29836.44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>778989-204-CM25</t>
+          <t>2429-1716-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>65.081.190-9</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>4223.58</v>
+        <v>11790.98</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2429-3130-CM25</t>
+          <t>2429-1718-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3553</v>
+        <v>12117.39</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1233623-1545-CM25</t>
+          <t>2429-1719-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>13387.34</v>
+        <v>19520.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2385-1215-CM25</t>
+          <t>1077908-51-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TECNOQUIM SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.378.846-6</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>859.54</v>
+        <v>859.41</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2385-1217-CM25</t>
+          <t>2385-202-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>851.73</v>
+        <v>9485.209999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2385-1218-CM25</t>
+          <t>1116003-10-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,27 +1744,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.362.622-7</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2738.78</v>
+        <v>865.75</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2429-3194-CM25</t>
+          <t>993-92-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>12206.38</v>
+        <v>11249.97</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1233623-1396-CM25</t>
+          <t>1233623-101-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1613.92</v>
+        <v>1221.91</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3858-23-CM26</t>
+          <t>2429-1815-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2306.68</v>
+        <v>5503.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2429-32-CM26</t>
+          <t>796305-30-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,27 +1988,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>40484.04</v>
+        <v>13547.28</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>707415-10-CM26</t>
+          <t>2429-1857-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1048.18</v>
+        <v>34184.37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3858-57-CM26</t>
+          <t>1346284-67-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,27 +2110,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.967.556-6</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>4191.42</v>
+        <v>1050.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2605-10-CM26</t>
+          <t>4291-290-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,27 +2171,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2178.97</v>
+        <v>2571.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2430-30-CM26</t>
+          <t>2385-295-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,27 +2232,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>31394.09</v>
+        <v>7669.52</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>778989-19-CM26</t>
+          <t>1233623-138-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>65.081.190-9</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIALIZADORA MERCEL SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>77.601.843-0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2446.79</v>
+        <v>4124.76</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2385-127-CM26</t>
+          <t>2429-1955-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,27 +2354,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2018.51</v>
+        <v>15671.31</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1113265-11-CM26</t>
+          <t>778989-74-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>62.000.770-6</t>
+          <t>65.081.190-9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2445.62</v>
+        <v>5608.53</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>769-128-CM26</t>
+          <t>778989-75-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>65.081.190-9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>18194.83</v>
+        <v>1712.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1079454-65-CM26</t>
+          <t>1697-119-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>7068.88</v>
+        <v>11350</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2429-254-CM26</t>
+          <t>3506-358-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2614.11</v>
+        <v>6341.43</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1288419-18-CM26</t>
+          <t>1233623-169-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,27 +2659,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gestión del Riesgo de Desastres</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>INVERSIONES CHILE LIMITADA</t>
+          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.795.374-5</t>
+          <t>76.967.556-6</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>37110.02</v>
+        <v>2527.66</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>993-49-CM26</t>
+          <t>2429-2018-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1753.36</v>
+        <v>18464.08</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2385-193-CM26</t>
+          <t>3858-209-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>10630.38</v>
+        <v>3304.47</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3506-219-CM26</t>
+          <t>3916-254-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,27 +2842,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>14860.01</v>
+        <v>3823.25</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3506-220-CM26</t>
+          <t>558869-103-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1112.28</v>
+        <v>5504.29</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2429-347-CM26</t>
+          <t>2429-2096-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,17 +2964,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>13771.67</v>
+        <v>1652.63</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>778989-66-CM26</t>
+          <t>2429-2112-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,27 +3025,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>65.081.190-9</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>886.0599999999999</v>
+        <v>15653.7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>778989-69-CM26</t>
+          <t>769-4518-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>65.081.190-9</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2457.51</v>
+        <v>19338.33</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3246-118-CM26</t>
+          <t>769-4584-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,27 +3147,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.103.019-3</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>ALA BASE N°1</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>823.73</v>
+        <v>7241.38</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3246-117-CM26</t>
+          <t>1697-153-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.103.019-3</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>ALA BASE N°1</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>7898.48</v>
+        <v>894.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2429-500-CM26</t>
+          <t>4291-974-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,27 +3269,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>25664.04</v>
+        <v>1439.48</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1697-124-CM26</t>
+          <t>2605-35-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>78.610.360-6</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>12033.97</v>
+        <v>3411.02</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1261592-490-CM26</t>
+          <t>2429-2254-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,27 +3391,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>12961.15</v>
+        <v>23034.32</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2385-365-CM26</t>
+          <t>2429-2265-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>32166.89</v>
+        <v>4197.34</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2429-578-CM26</t>
+          <t>2429-2266-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,17 +3513,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>12.364.273-2</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>5744.42</v>
+        <v>2801.68</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>769-320-CM26</t>
+          <t>2385-548-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>8608.48</v>
+        <v>53738.27</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2429-614-CM26</t>
+          <t>2605-37-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3635,17 +3635,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.967.556-6</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>3739.13</v>
+        <v>934.48</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1116003-22-CM26</t>
+          <t>4291-1383-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>QUALITY RUBBER S.A.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.097.502-8</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>8813.530000000001</v>
+        <v>8231.58</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1116003-23-CM26</t>
+          <t>2429-2392-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>LORENZINI PAGLIETTINI Y CIA LTDA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>80.565.500-3</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>12002.02</v>
+        <v>13432.63</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2429-666-CM26</t>
+          <t>650-67-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.814.000-8</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>27898.02</v>
+        <v>1122.71</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1079454-263-CM26</t>
+          <t>650-69-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3879,27 +3879,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.814.000-8</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>78.610.360-6</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>781.13</v>
+        <v>2138.51</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>778992-183-CM26</t>
+          <t>930-236-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3940,27 +3940,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>4835.17</v>
+        <v>756.27</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>930-139-CM26</t>
+          <t>2605-57-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>817.29</v>
+        <v>927.89</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4051-140-CM26</t>
+          <t>3506-600-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,7 +4107,5314 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
+        <v>1752.54</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>3506-598-CM25</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>69.020.100-3</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>20750.94</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1775-38-CM25</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>60.804.004-8</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>997.96</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2385-744-CM25</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>BLOOMBERRY COMERCIAL SPA</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>76.330.742-5</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>13405.77</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2429-2525-CM25</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>9952.91</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1775-42-CM25</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>60.804.004-8</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>76.178.855-8</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>11061.67</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>778989-160-CM25</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>65.081.190-9</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>825.48</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2258-22640-CM25</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>1992.58</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2605-60-CM25</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>2052.45</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>769-4837-CM25</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>61.606.200-k</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>25029.1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>558869-203-CM25</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>1406.52</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>558869-204-CM25</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>27893.63</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>697036-89-CM25</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>1108.35</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2385-935-CM25</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>10907.55</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>3834-245-CM25</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>15775.14</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>650-108-CM25</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>61.814.000-8</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>3537.46</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>558869-227-CM25</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Francisco javier</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>76.882.403-7</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>1524.07</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>558869-229-CM25</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>SEGURYCEL SA</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>99.510.910-7</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>5593.81</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>558869-233-CM25</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>1071.21</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1417-108-CM25</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>61.104.000-8</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>76.178.855-8</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>10139.17</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2385-986-CM25</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>14473.94</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2430-324-CM25</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>23072.95</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2385-1002-CM25</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>13217.47</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>4291-2371-CM25</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>70.791.800-4</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>9130.83</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2429-2776-CM25</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>19166.41</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1116003-48-CM25</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>61.104.000-8</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>76.178.855-8</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>5387.23</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>930-314-CM25</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>COMERCIAL ROYA WOLF SPA</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>77.038.841-4</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>1011.27</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>3834-271-CM25</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>21744.29</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>3834-275-CM25</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>5366.3</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2429-2957-CM25</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>28997.36</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1775-67-CM25</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>60.804.004-8</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>DIRECCIÓN REGIONAL ADUANA DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>76.178.855-8</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>8624.530000000001</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2429-2971-CM25</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>26826.59</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1230848-314-CM25</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>70.954.900-6</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>1632.58</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2429-2993-CM25</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>15321.06</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1077908-315-CM25</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>62.000.380-8</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>MALMO S.A.</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>76.195.558-6</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>1040.02</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1983-89-CM25</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>60.701.011-0</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Servicio Nacional de Pesca y Acuicultura</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>76.178.855-8</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>2644.13</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1775-73-CM25</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>60.804.004-8</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>DIRECCIÓN REGIONAL ADUANA DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>76.178.855-8</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>8815.01</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>778989-204-CM25</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>65.081.190-9</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>3a Briagada Acorazada "La Concepción"</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>SODIMAC S.A.</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>4223.58</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2429-3130-CM25</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>76.178.855-8</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>3553</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1233623-1545-CM25</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>76.178.855-8</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>13387.34</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2385-1215-CM25</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>TECNOQUIM SPA</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>76.378.846-6</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>859.54</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2385-1217-CM25</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>851.73</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2385-1218-CM25</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>77.362.622-7</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>2738.78</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2429-3194-CM25</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>12206.38</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>1233623-1396-CM25</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>76.178.855-8</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>1613.92</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>3858-23-CM26</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>2306.68</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2429-32-CM26</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>40484.04</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>707415-10-CM26</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>1048.18</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>3858-57-CM26</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>4191.42</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2605-10-CM26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>SOSEG SPA</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>76.897.534-5</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>2178.97</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2430-30-CM26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>31394.09</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>778989-19-CM26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>65.081.190-9</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>3a Briagada Acorazada "La Concepción"</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>2446.79</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2385-127-CM26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Comercial Agustin Limitada</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>2018.51</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>769-128-CM26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>61.606.200-k</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>18194.83</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>1113265-11-CM26</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>62.000.770-6</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>2445.62</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1079454-65-CM26</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>61.978.660-2</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS II ZONA</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>7068.88</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2429-254-CM26</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>2614.11</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1288419-18-CM26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>69.252.500-0</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Gestión del Riesgo de Desastres</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>INVERSIONES CHILE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>77.795.374-5</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>37110.02</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>993-49-CM26</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>1753.36</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2385-193-CM26</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>76.178.855-8</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>10630.38</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>3506-219-CM26</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>69.020.100-3</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>14860.01</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>3506-220-CM26</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>69.020.100-3</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>1112.28</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2429-347-CM26</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>13771.67</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>778989-66-CM26</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>65.081.190-9</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>3a Briagada Acorazada "La Concepción"</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>886.0599999999999</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>778989-69-CM26</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>65.081.190-9</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>3a Briagada Acorazada "La Concepción"</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>2457.51</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>3246-118-CM26</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>61.103.019-3</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>ALA BASE N°1</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>823.73</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>3246-117-CM26</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>61.103.019-3</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>ALA BASE N°1</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA WAY SPA</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>76.532.399-1</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>7898.48</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2429-500-CM26</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>25664.04</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>1697-124-CM26</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>12033.97</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>1261592-490-CM26</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>12961.15</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2385-365-CM26</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>32166.89</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2429-578-CM26</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>5744.42</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>769-320-CM26</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>61.606.200-k</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>8608.48</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2429-614-CM26</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>3739.13</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>1116003-23-CM26</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>61.104.000-8</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>LORENZINI PAGLIETTINI Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>80.565.500-3</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>12002.02</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>1116003-22-CM26</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>61.104.000-8</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>8813.530000000001</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2429-666-CM26</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>27898.02</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>1079454-263-CM26</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>61.978.660-2</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS II ZONA</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>781.13</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>778992-183-CM26</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>61.953.000-4</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>4835.17</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>930-139-CM26</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>817.29</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>4051-140-CM26</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>69.252.600-7</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>SOSEG SPA</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>76.897.534-5</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="n">
         <v>1117.63</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>1346284-149-CM26</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>4004.2</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>993-172-CM26</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>29501.56</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2605-64-CM26</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>SODIMAC S.A.</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>4444.49</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>769-600-CM26</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>61.606.200-k</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>17586.15</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2385-654-CM26</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>12.364.273-2</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="n">
+        <v>9560.469999999999</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>993-199-CM26</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="n">
+        <v>1721.37</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>769-605-CM26</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>61.606.200-k</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="n">
+        <v>3432.37</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/antofagasta.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M147"/>
+  <dimension ref="A1:M149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5211,7 +5211,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1417-108-CM25</t>
+          <t>2385-986-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>10139.17</v>
+        <v>14473.94</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2385-986-CM25</t>
+          <t>2430-324-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>14473.94</v>
+        <v>23072.95</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2430-324-CM25</t>
+          <t>1417-108-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>23072.95</v>
+        <v>10139.17</v>
       </c>
     </row>
     <row r="82">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Gestión del Riesgo de Desastres</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>ALA BASE N°1</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>ALA BASE N°1</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8566,7 +8566,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1116003-23-CM26</t>
+          <t>1116003-22-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>LORENZINI PAGLIETTINI Y CIA LTDA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>80.565.500-3</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>12002.02</v>
+        <v>8813.530000000001</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1116003-22-CM26</t>
+          <t>1116003-23-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>LORENZINI PAGLIETTINI Y CIA LTDA</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>80.565.500-3</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>8813.530000000001</v>
+        <v>12002.02</v>
       </c>
     </row>
     <row r="136">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8810,7 +8810,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>778992-183-CM26</t>
+          <t>930-139-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8825,22 +8825,22 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8865,13 +8865,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>4835.17</v>
+        <v>817.29</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>930-139-CM26</t>
+          <t>4051-140-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8886,22 +8886,22 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>817.29</v>
+        <v>1117.63</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>4051-140-CM26</t>
+          <t>2429-907-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8947,22 +8947,22 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1117.63</v>
+        <v>38414.77</v>
       </c>
     </row>
     <row r="141">
@@ -9415,6 +9415,128 @@
       </c>
       <c r="M147" s="2" t="n">
         <v>3432.37</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2429-1128-CM26</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>1297.44</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2430-339-CM26</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>28260.23</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/antofagasta.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/antofagasta.xlsx
@@ -1172,7 +1172,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2213,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2339,11 @@
           <t>77.601.843-0</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3136,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3201,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3266,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4063,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4677,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4742,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5478,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5543,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6096,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6588,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6653,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6718,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +6905,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7397,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7645,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8076,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8141,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8206,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8393,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8580,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8645,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8710,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9141,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9206,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9332,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9458,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9523,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/antofagasta.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/antofagasta.xlsx
@@ -2465,7 +2465,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4250,7 +4254,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7336,7 +7344,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/antofagasta.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M149"/>
+  <dimension ref="A1:M154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1311,7 +1311,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2605-7-CM25</t>
+          <t>2430-45-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1386.53</v>
+        <v>29836.44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2430-45-CM25</t>
+          <t>2605-7-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>29836.44</v>
+        <v>1386.53</v>
       </c>
     </row>
     <row r="17">
@@ -3836,7 +3836,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>650-67-CM25</t>
+          <t>650-69-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3876,12 +3876,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>78.610.360-6</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3891,13 +3891,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1122.71</v>
+        <v>2138.51</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>650-69-CM25</t>
+          <t>650-67-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>78.610.360-6</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3952,7 +3952,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2138.51</v>
+        <v>1122.71</v>
       </c>
     </row>
     <row r="58">
@@ -4019,7 +4019,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2605-57-CM25</t>
+          <t>3506-598-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4039,17 +4039,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4059,32 +4059,28 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>927.89</v>
+        <v>20750.94</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3506-600-CM25</t>
+          <t>2605-57-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4104,17 +4100,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4124,28 +4120,32 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1752.54</v>
+        <v>927.89</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3506-598-CM25</t>
+          <t>3506-600-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>20750.94</v>
+        <v>1752.54</v>
       </c>
     </row>
     <row r="62">
@@ -4950,7 +4950,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3834-245-CM25</t>
+          <t>650-108-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4975,12 +4975,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.814.000-8</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -5005,13 +5005,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>15775.14</v>
+        <v>3537.46</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>650-108-CM25</t>
+          <t>3834-245-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.814.000-8</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5066,7 +5066,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>3537.46</v>
+        <v>15775.14</v>
       </c>
     </row>
     <row r="76">
@@ -5316,7 +5316,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2430-324-CM25</t>
+          <t>1417-108-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5336,17 +5336,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5371,13 +5371,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>23072.95</v>
+        <v>10139.17</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1417-108-CM25</t>
+          <t>2430-324-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5397,17 +5397,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5417,12 +5417,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>10139.17</v>
+        <v>23072.95</v>
       </c>
     </row>
     <row r="82">
@@ -7361,7 +7361,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>769-128-CM26</t>
+          <t>1113265-11-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>62.000.770-6</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7401,32 +7401,28 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>18194.83</v>
+        <v>2445.62</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1113265-11-CM26</t>
+          <t>769-128-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7451,12 +7447,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>62.000.770-6</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7466,22 +7462,26 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2445.62</v>
+        <v>18194.83</v>
       </c>
     </row>
     <row r="115">
@@ -7796,7 +7796,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3506-219-CM26</t>
+          <t>3506-220-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7851,13 +7851,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>14860.01</v>
+        <v>1112.28</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3506-220-CM26</t>
+          <t>3506-219-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7912,7 +7912,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1112.28</v>
+        <v>14860.01</v>
       </c>
     </row>
     <row r="122">
@@ -9422,7 +9422,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>993-199-CM26</t>
+          <t>769-605-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9442,17 +9442,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -9481,13 +9481,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1721.37</v>
+        <v>3432.37</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>769-605-CM26</t>
+          <t>993-199-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9507,17 +9507,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9527,12 +9527,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -9546,7 +9546,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>3432.37</v>
+        <v>1721.37</v>
       </c>
     </row>
     <row r="148">
@@ -9613,62 +9613,379 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
+          <t>3506-715-CM26</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>69.020.100-3</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>17201.09</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
           <t>2430-339-CM26</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>2239-9-LR23</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="D150" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
+      <c r="E150" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="F150" t="inlineStr">
         <is>
           <t>69.020.300-6</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
+      <c r="G150" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
         <is>
           <t>LUIS ALEXANDER</t>
         </is>
       </c>
-      <c r="J149" t="inlineStr">
+      <c r="J150" t="inlineStr">
         <is>
           <t>76.962.756-1</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M149" s="2" t="n">
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="n">
         <v>28260.23</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2605-84-CM26</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>SOSEG SPA</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>76.897.534-5</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="n">
+        <v>1850.27</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2605-82-CM26</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="n">
+        <v>8495.110000000001</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>650-144-CM26</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>61.814.000-8</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="n">
+        <v>3611.55</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>1261592-1450-CM26</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="n">
+        <v>20393.91</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/antofagasta.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/antofagasta.xlsx
@@ -9125,7 +9125,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/antofagasta.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M154"/>
+  <dimension ref="A1:M155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7361,7 +7361,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1113265-11-CM26</t>
+          <t>769-128-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>62.000.770-6</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7401,28 +7401,32 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2445.62</v>
+        <v>18194.83</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>769-128-CM26</t>
+          <t>1113265-11-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7447,12 +7451,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>62.000.770-6</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7462,26 +7466,22 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>18194.83</v>
+        <v>2445.62</v>
       </c>
     </row>
     <row r="115">
@@ -7796,7 +7796,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3506-220-CM26</t>
+          <t>3506-219-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7851,13 +7851,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>1112.28</v>
+        <v>14860.01</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3506-219-CM26</t>
+          <t>3506-220-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7912,7 +7912,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>14860.01</v>
+        <v>1112.28</v>
       </c>
     </row>
     <row r="122">
@@ -9926,65 +9926,126 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
+          <t>1261592-1444-CM26</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="n">
+        <v>3712.47</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
           <t>1261592-1450-CM26</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>2239-9-LR23</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
+      <c r="D155" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="E155" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
+      <c r="F155" t="inlineStr">
         <is>
           <t>71.102.600-2</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
+      <c r="G155" t="inlineStr">
         <is>
           <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
         <is>
           <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
-      <c r="J154" t="inlineStr">
+      <c r="J155" t="inlineStr">
         <is>
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
+      <c r="K155" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M154" s="2" t="n">
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="n">
         <v>20393.91</v>
       </c>
     </row>
